--- a/branch_details.xlsx
+++ b/branch_details.xlsx
@@ -418,7 +418,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>지점이름</t>
+          <t>지점_이름</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -435,7 +435,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Fairway</t>
+          <t>San Jose</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -452,7 +452,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lammas</t>
+          <t>GREAT BARTON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>Hamilton</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -486,7 +486,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marlin</t>
+          <t>JERRAWA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Pasewalker</t>
+          <t>Rudersberg</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -520,7 +520,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Toftvej</t>
+          <t>København K</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -537,7 +537,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Revolucion</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -554,7 +554,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Old Dear Lane</t>
+          <t>Poughkeepsie</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Pineview</t>
+          <t>Elgin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -588,7 +588,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Vesta</t>
+          <t>Oak Brook</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -605,7 +605,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bluff</t>
+          <t>Annapolis Junction</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jett</t>
+          <t>Los Angeles</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Arlington</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -656,7 +656,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plainfield</t>
+          <t>Syracuse</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -673,7 +673,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Thunder</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -690,7 +690,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Junkins</t>
+          <t>Valdosta</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -707,7 +707,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Poplar</t>
+          <t>Hialeah</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Straford</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Custer</t>
+          <t>Johnsonburg</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -758,7 +758,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kita</t>
+          <t>Hokkaido</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Port Chester</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -792,7 +792,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -809,7 +809,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Vientos</t>
+          <t>Villaluenga del Rosario</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -826,7 +826,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>King Street</t>
+          <t>London</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>New Road</t>
+          <t>GLOUCESTER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -860,7 +860,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>George</t>
+          <t>NEWPORT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>The Green</t>
+          <t>TAUNTON</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -894,7 +894,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Springfield</t>
+          <t>SOUTHEND-ON-SEA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Highfield</t>
+          <t>SHEFFIELD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -928,7 +928,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Albert</t>
+          <t>HULL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Church</t>
+          <t>SHREWSBURY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Don Jackson</t>
+          <t>Honolulu</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bombardier</t>
+          <t>Wayne</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1013,7 +1013,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Courtright</t>
+          <t>Milton</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1030,7 +1030,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>The Grove</t>
+          <t>NEWCASTLE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1047,7 +1047,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>BRISTOL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1064,7 +1064,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Broadway</t>
+          <t>BOURNEMOUTH</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Green Lane</t>
+          <t>LEICESTER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>New Road</t>
+          <t>SUNDERLAND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1115,7 +1115,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>North Street</t>
+          <t>BOLTON</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>King Street</t>
+          <t>SOUTHAMPTON</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1149,7 +1149,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Highfield</t>
+          <t>BLACKPOOL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1166,7 +1166,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Street</t>
+          <t>DARLINGTON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Main Road</t>
+          <t>LIVERPOOL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1200,7 +1200,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Park Lane</t>
+          <t>MANCHESTER</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1217,7 +1217,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kings Road</t>
+          <t>SHEFFIELD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1234,7 +1234,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Mill</t>
+          <t>BOLTON</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>SWANSEA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1268,7 +1268,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Mill Lane</t>
+          <t>LEEDS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>York Road</t>
+          <t>SWANSEA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1302,7 +1302,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>West Street</t>
+          <t>CARDIFF</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>New Road</t>
+          <t>LEICESTER</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1336,7 +1336,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Main Street</t>
+          <t>SOUTHAMPTON</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Stanley Road</t>
+          <t>IPSWICH</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ebisu</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Gongdeok</t>
+          <t>Seoul</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
